--- a/public/templates/official-works-template.xlsx
+++ b/public/templates/official-works-template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:S2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -414,10 +414,11 @@
     <col min="12" max="12" width="12.83203125" customWidth="1"/>
     <col min="13" max="13" width="12.83203125" customWidth="1"/>
     <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="18.83203125" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
     <col min="17" max="17" width="12.83203125" customWidth="1"/>
     <col min="18" max="18" width="12.83203125" customWidth="1"/>
+    <col min="19" max="19" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -443,36 +444,39 @@
         <v>연령등급</v>
       </c>
       <c r="H1" t="str">
+        <v>OTT</v>
+      </c>
+      <c r="I1" t="str">
         <v>시작일</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>종료일</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>분기</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>화수</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>제작사</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>감독</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>원작자</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>AniList ID</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>소개</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>상태</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>우선순위</v>
       </c>
     </row>
@@ -499,55 +503,58 @@
         <v>15세 이상</v>
       </c>
       <c r="H2" t="str">
+        <v>Laftel, TVING, Wavve</v>
+      </c>
+      <c r="I2" t="str">
         <v>2026-04-01</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>2026-06-24</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>2026 2분기</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>12</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>Sample Studio</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>홍길동</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>원작자명</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>12345</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
         <v>Short synopsis or key premise.</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="R2" t="str">
         <v>DRAFT</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="32.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -688,194 +695,211 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>시작일</v>
+        <v>OTT</v>
       </c>
       <c r="B9" t="str">
         <v>N</v>
       </c>
       <c r="C9" t="str">
-        <v>Air or publication start date. Leave blank if uncertain.</v>
+        <v>Domestic streaming services available to Korean users. Separate multiple values with commas.</v>
       </c>
       <c r="D9" t="str">
-        <v>YYYY-MM-DD</v>
+        <v>comma-separated text</v>
       </c>
       <c r="E9" t="str">
-        <v>1999-10-20</v>
+        <v>Laftel, TVING, Wavve, Coupang Play, Netflix, Disney+, Watcha, Series On</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>종료일</v>
+        <v>시작일</v>
       </c>
       <c r="B10" t="str">
         <v>N</v>
       </c>
       <c r="C10" t="str">
-        <v>End date. Leave blank if ongoing or unknown.</v>
+        <v>Air or publication start date. Leave blank if uncertain.</v>
       </c>
       <c r="D10" t="str">
         <v>YYYY-MM-DD</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-06-24</v>
+        <v>1999-10-20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>분기</v>
+        <v>종료일</v>
       </c>
       <c r="B11" t="str">
         <v>N</v>
       </c>
       <c r="C11" t="str">
-        <v>Season/cour label for discovery and filtering.</v>
+        <v>End date. Leave blank if ongoing or unknown.</v>
       </c>
       <c r="D11" t="str">
-        <v>text</v>
+        <v>YYYY-MM-DD</v>
       </c>
       <c r="E11" t="str">
-        <v>2026 2분기</v>
+        <v>2026-06-24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>화수</v>
+        <v>분기</v>
       </c>
       <c r="B12" t="str">
         <v>N</v>
       </c>
       <c r="C12" t="str">
-        <v>Total episode count. Number only.</v>
+        <v>Season/cour label for discovery and filtering.</v>
       </c>
       <c r="D12" t="str">
-        <v>number</v>
-      </c>
-      <c r="E12">
-        <v>12</v>
+        <v>text</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2026 2분기</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>제작사</v>
+        <v>화수</v>
       </c>
       <c r="B13" t="str">
         <v>N</v>
       </c>
       <c r="C13" t="str">
-        <v>Production studios. Separate multiple values with commas.</v>
+        <v>Total episode count. Number only.</v>
       </c>
       <c r="D13" t="str">
-        <v>comma-separated text</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Toei Animation</v>
+        <v>number</v>
+      </c>
+      <c r="E13">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>감독</v>
+        <v>제작사</v>
       </c>
       <c r="B14" t="str">
         <v>N</v>
       </c>
       <c r="C14" t="str">
-        <v>Director name.</v>
+        <v>Production studios. Separate multiple values with commas.</v>
       </c>
       <c r="D14" t="str">
-        <v>text</v>
+        <v>comma-separated text</v>
       </c>
       <c r="E14" t="str">
-        <v>Konosuke Uda</v>
+        <v>Toei Animation</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>원작자</v>
+        <v>감독</v>
       </c>
       <c r="B15" t="str">
         <v>N</v>
       </c>
       <c r="C15" t="str">
-        <v>Original creator or author.</v>
+        <v>Director name.</v>
       </c>
       <c r="D15" t="str">
         <v>text</v>
       </c>
       <c r="E15" t="str">
-        <v>Eiichiro Oda</v>
+        <v>Konosuke Uda</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>AniList ID</v>
+        <v>원작자</v>
       </c>
       <c r="B16" t="str">
         <v>N</v>
       </c>
       <c r="C16" t="str">
-        <v>AniList media ID. Number only.</v>
+        <v>Original creator or author.</v>
       </c>
       <c r="D16" t="str">
-        <v>number</v>
-      </c>
-      <c r="E16">
-        <v>21</v>
+        <v>text</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Eiichiro Oda</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>소개</v>
+        <v>AniList ID</v>
       </c>
       <c r="B17" t="str">
         <v>N</v>
       </c>
       <c r="C17" t="str">
-        <v>Short synopsis. Prefer concise, factual description.</v>
+        <v>AniList media ID. Number only.</v>
       </c>
       <c r="D17" t="str">
-        <v>text</v>
-      </c>
-      <c r="E17" t="str">
-        <v>Adventure story about a boy who wants to become Pirate King.</v>
+        <v>number</v>
+      </c>
+      <c r="E17">
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>상태</v>
+        <v>소개</v>
       </c>
       <c r="B18" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="C18" t="str">
-        <v>Catalog visibility state. Use DRAFT before publishing.</v>
+        <v>Short synopsis. Prefer concise, factual description.</v>
       </c>
       <c r="D18" t="str">
-        <v>DRAFT | PUBLISHED | HIDDEN</v>
+        <v>text</v>
       </c>
       <c r="E18" t="str">
-        <v>DRAFT</v>
+        <v>Adventure story about a boy who wants to become Pirate King.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
+        <v>상태</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Y</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Catalog visibility state. Use DRAFT before publishing.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>DRAFT | PUBLISHED | HIDDEN</v>
+      </c>
+      <c r="E19" t="str">
+        <v>DRAFT</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>우선순위</v>
       </c>
-      <c r="B19" t="str">
-        <v>N</v>
-      </c>
-      <c r="C19" t="str">
+      <c r="B20" t="str">
+        <v>N</v>
+      </c>
+      <c r="C20" t="str">
         <v>Sort priority. Lower numbers appear earlier.</v>
       </c>
-      <c r="D19" t="str">
+      <c r="D20" t="str">
         <v>number</v>
       </c>
-      <c r="E19">
+      <c r="E20">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E20"/>
   </ignoredErrors>
 </worksheet>
 </file>